--- a/storage/app/Colombo_masterlist_upload.xlsx
+++ b/storage/app/Colombo_masterlist_upload.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Remark</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -726,8 +732,12 @@
       <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="B3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
